--- a/data/trans_orig/Q5411-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2007</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9226</t>
+          <t>9077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28900</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65391</t>
+          <t>65540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73691</t>
+          <t>73681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19283</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>60638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79815</t>
+          <t>80254</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92804</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145246</t>
+          <t>144563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158444</t>
+          <t>158564</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43048</t>
+          <t>43135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>50050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65511</t>
+          <t>65659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78873</t>
+          <t>77895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112896</t>
+          <t>112589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127181</t>
+          <t>126946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51060</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>59994</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70987</t>
+          <t>71024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>113283</t>
+          <t>114318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125122</t>
+          <t>125606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>19502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26905</t>
+          <t>27374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>37879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>51091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63769</t>
+          <t>63971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38901</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57490</t>
+          <t>56598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67971</t>
+          <t>67795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99758</t>
+          <t>99394</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113146</t>
+          <t>112299</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15994</t>
+          <t>15428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97444</t>
+          <t>97699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105007</t>
+          <t>105072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105818</t>
+          <t>105491</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115184</t>
+          <t>115166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207055</t>
+          <t>207621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218761</t>
+          <t>219262</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>26592</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36513</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95954</t>
+          <t>95268</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>108036</t>
+          <t>107565</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127618</t>
+          <t>126633</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143560</t>
+          <t>143538</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>228605</t>
+          <t>226165</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>249321</t>
+          <t>247848</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50678</t>
+          <t>50278</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>82380</t>
+          <t>82118</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75512</t>
+          <t>74520</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113593</t>
+          <t>111553</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>462405</t>
+          <t>463339</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>482739</t>
+          <t>482626</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>594462</t>
+          <t>594724</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>626164</t>
+          <t>626564</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1065715</t>
+          <t>1067755</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1103796</t>
+          <t>1104788</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2012</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21613</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36972</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43461</t>
+          <t>44281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40470</t>
+          <t>40267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67077</t>
+          <t>68471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82737</t>
+          <t>83120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37441</t>
+          <t>37404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26064</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49714</t>
+          <t>48672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60958</t>
+          <t>59285</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74885</t>
+          <t>74843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64652</t>
+          <t>64689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83071</t>
+          <t>83565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131582</t>
+          <t>132624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155232</t>
+          <t>155335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25464</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40749</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>52536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54504</t>
+          <t>53729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>100258</t>
+          <t>99691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118559</t>
+          <t>118705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37645</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49523</t>
+          <t>49335</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60766</t>
+          <t>60683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58254</t>
+          <t>58168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73897</t>
+          <t>73472</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111957</t>
+          <t>111713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131650</t>
+          <t>130691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8151</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28544</t>
+          <t>28674</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>29288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41825</t>
+          <t>41704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>52793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68615</t>
+          <t>68320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36438</t>
+          <t>36164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37944</t>
+          <t>37903</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48533</t>
+          <t>48536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42892</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57533</t>
+          <t>57382</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85530</t>
+          <t>85804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104556</t>
+          <t>103661</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20938</t>
+          <t>21839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41384</t>
+          <t>42027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32441</t>
+          <t>32270</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>56834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89118</t>
+          <t>89031</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105230</t>
+          <t>105096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100578</t>
+          <t>99935</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>121024</t>
+          <t>120123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197100</t>
+          <t>197392</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>221785</t>
+          <t>221956</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>14441</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34299</t>
+          <t>32306</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>18410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40099</t>
+          <t>39581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>109076</t>
+          <t>108931</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118686</t>
+          <t>118664</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>130118</t>
+          <t>132111</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149761</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>245070</t>
+          <t>245588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267118</t>
+          <t>266759</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>46769</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80660</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>141120</t>
+          <t>141800</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>187453</t>
+          <t>188729</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>199473</t>
+          <t>197047</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>253902</t>
+          <t>255925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>478977</t>
+          <t>482159</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>512868</t>
+          <t>514686</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>555522</t>
+          <t>554246</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>601855</t>
+          <t>601175</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1048710</t>
+          <t>1046687</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1103139</t>
+          <t>1105565</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2016</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>17239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>25623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36404</t>
+          <t>36427</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43844</t>
+          <t>43747</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62961</t>
+          <t>62664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78245</t>
+          <t>77905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30397</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77780</t>
+          <t>77300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85855</t>
+          <t>85679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90257</t>
+          <t>89903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107376</t>
+          <t>107255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172126</t>
+          <t>171035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191044</t>
+          <t>191218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55775</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62778</t>
+          <t>62773</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66075</t>
+          <t>65912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78620</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125716</t>
+          <t>126600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139943</t>
+          <t>139864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29932</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>51370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60683</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69619</t>
+          <t>71127</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85644</t>
+          <t>85521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126353</t>
+          <t>125355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144293</t>
+          <t>143830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36806</t>
+          <t>37411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47355</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77970</t>
+          <t>77761</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>89364</t>
+          <t>89254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12620</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>24277</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32161</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>35520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45195</t>
+          <t>45170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43636</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59186</t>
+          <t>58972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83673</t>
+          <t>83167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101919</t>
+          <t>101879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34984</t>
+          <t>35207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50122</t>
+          <t>48449</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>92530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105492</t>
+          <t>105505</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>112641</t>
+          <t>112418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>131970</t>
+          <t>132210</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>209688</t>
+          <t>211361</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233763</t>
+          <t>233713</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15169</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22731</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31623</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118999</t>
+          <t>119247</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130777</t>
+          <t>131052</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153566</t>
+          <t>153753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169596</t>
+          <t>169411</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278842</t>
+          <t>278626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>298196</t>
+          <t>297771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60470</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>80874</t>
+          <t>84091</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>123926</t>
+          <t>126267</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>126324</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>178156</t>
+          <t>174546</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>530858</t>
+          <t>530466</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>554323</t>
+          <t>555447</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>654005</t>
+          <t>651664</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>697057</t>
+          <t>693840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1191103</t>
+          <t>1194713</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1242066</t>
+          <t>1242935</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2023</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47387</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54432</t>
+          <t>54383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49335</t>
+          <t>48553</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57635</t>
+          <t>57871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99031</t>
+          <t>99891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110919</t>
+          <t>110775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32114</t>
+          <t>33492</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25222</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66609</t>
+          <t>66832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77032</t>
+          <t>76508</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>96878</t>
+          <t>95500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110361</t>
+          <t>110215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167221</t>
+          <t>166581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184478</t>
+          <t>183839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>20404</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33431</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66020</t>
+          <t>65551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67796</t>
+          <t>67448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77920</t>
+          <t>77673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127484</t>
+          <t>127250</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140651</t>
+          <t>140511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,32%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24991</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68140</t>
+          <t>68004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73976</t>
+          <t>73907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>81882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91184</t>
+          <t>91232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153312</t>
+          <t>153100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163524</t>
+          <t>163940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45046</t>
+          <t>45682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52457</t>
+          <t>52357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74210</t>
+          <t>74172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83143</t>
+          <t>83036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,61%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51855</t>
+          <t>51960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57573</t>
+          <t>57551</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47289</t>
+          <t>47190</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55129</t>
+          <t>55187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101578</t>
+          <t>101555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110988</t>
+          <t>110975</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14613</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55983</t>
+          <t>54589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54900</t>
+          <t>52892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108641</t>
+          <t>109541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119168</t>
+          <t>119776</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>282598</t>
+          <t>283992</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>333342</t>
+          <t>334179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406936</t>
+          <t>408944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>453904</t>
+          <t>454034</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>17637</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23212</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137778</t>
+          <t>137776</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144918</t>
+          <t>144661</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>168832</t>
+          <t>169005</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>179059</t>
+          <t>178856</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>310510</t>
+          <t>310349</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>322075</t>
+          <t>321941</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>38817</t>
+          <t>39462</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61917</t>
+          <t>61756</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>68918</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>155659</t>
+          <t>156864</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114521</t>
+          <t>110236</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>201090</t>
+          <t>201182</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>588261</t>
+          <t>588422</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>611361</t>
+          <t>610716</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>877179</t>
+          <t>875974</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>967624</t>
+          <t>963920</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1481926</t>
+          <t>1481834</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1568495</t>
+          <t>1572780</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5411-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34582</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73681</t>
+          <t>73585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19966</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60638</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80254</t>
+          <t>79974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92718</t>
+          <t>92748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>144832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158564</t>
+          <t>158358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43135</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50050</t>
+          <t>50047</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65659</t>
+          <t>65449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77895</t>
+          <t>78890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112589</t>
+          <t>113573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126946</t>
+          <t>127096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59994</t>
+          <t>59117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>70964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114318</t>
+          <t>114377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125606</t>
+          <t>125571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>19359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27374</t>
+          <t>27165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37879</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51091</t>
+          <t>51234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63971</t>
+          <t>64196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37961</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46258</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56598</t>
+          <t>57246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67795</t>
+          <t>67979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99394</t>
+          <t>100876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112299</t>
+          <t>112693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15428</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97699</t>
+          <t>98064</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105072</t>
+          <t>105096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105491</t>
+          <t>106091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115166</t>
+          <t>115119</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>207320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>219262</t>
+          <t>218568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>16236</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>26075</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>37496</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95268</t>
+          <t>95657</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107565</t>
+          <t>107310</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126633</t>
+          <t>127150</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143538</t>
+          <t>143830</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>226165</t>
+          <t>227622</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>247848</t>
+          <t>248584</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39127</t>
+          <t>39294</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50278</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>111553</t>
+          <t>110795</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>463339</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>482626</t>
+          <t>481695</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>594724</t>
+          <t>594513</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>626564</t>
+          <t>627369</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1067755</t>
+          <t>1068513</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1104788</t>
+          <t>1105564</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>24965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36769</t>
+          <t>36335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44281</t>
+          <t>43503</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40267</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68471</t>
+          <t>68210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83120</t>
+          <t>83011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>37307</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>26704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48672</t>
+          <t>50178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59285</t>
+          <t>60103</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74843</t>
+          <t>75121</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64689</t>
+          <t>64786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83565</t>
+          <t>83476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132624</t>
+          <t>131118</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155335</t>
+          <t>154592</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39590</t>
+          <t>39670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52536</t>
+          <t>52532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53729</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>69155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99691</t>
+          <t>99125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118705</t>
+          <t>117436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>27350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18911</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37889</t>
+          <t>37292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49335</t>
+          <t>49674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60683</t>
+          <t>60621</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>58224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73472</t>
+          <t>73310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111713</t>
+          <t>112310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130691</t>
+          <t>131305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28674</t>
+          <t>29928</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>29227</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29288</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41704</t>
+          <t>42629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>51539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68320</t>
+          <t>68192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27446</t>
+          <t>26740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36164</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37903</t>
+          <t>36857</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48536</t>
+          <t>48528</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42766</t>
+          <t>43472</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57382</t>
+          <t>58004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85804</t>
+          <t>86563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103661</t>
+          <t>104653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21839</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>41829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32270</t>
+          <t>32027</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56834</t>
+          <t>57270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89031</t>
+          <t>88802</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105096</t>
+          <t>104801</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>99935</t>
+          <t>100133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120123</t>
+          <t>120853</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>197392</t>
+          <t>196956</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>221956</t>
+          <t>222199</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32306</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108931</t>
+          <t>108419</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118664</t>
+          <t>118645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>132111</t>
+          <t>131427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149976</t>
+          <t>149710</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>245588</t>
+          <t>245881</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>266759</t>
+          <t>265872</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>141800</t>
+          <t>140867</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>188729</t>
+          <t>186359</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>197047</t>
+          <t>196079</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>255925</t>
+          <t>251238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>482159</t>
+          <t>480863</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>514686</t>
+          <t>513169</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>554246</t>
+          <t>556616</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>601175</t>
+          <t>602108</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1046687</t>
+          <t>1051374</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1105565</t>
+          <t>1106533</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27593</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36427</t>
+          <t>36445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43747</t>
+          <t>44551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62664</t>
+          <t>62944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77905</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>25557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31488</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77300</t>
+          <t>76622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85679</t>
+          <t>85547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89903</t>
+          <t>89671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107255</t>
+          <t>107257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171035</t>
+          <t>171855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191218</t>
+          <t>190611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54044</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62773</t>
+          <t>62775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65912</t>
+          <t>66189</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77982</t>
+          <t>78618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126600</t>
+          <t>126357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>139864</t>
+          <t>139492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30930</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51370</t>
+          <t>51478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60753</t>
+          <t>60579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71127</t>
+          <t>70495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85521</t>
+          <t>86380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125355</t>
+          <t>125271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143830</t>
+          <t>144226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>12923</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48108</t>
+          <t>48208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77761</t>
+          <t>78363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>89254</t>
+          <t>89500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24277</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>36723</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45170</t>
+          <t>45307</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83167</t>
+          <t>83255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101879</t>
+          <t>102042</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>20025</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48449</t>
+          <t>49238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92530</t>
+          <t>92160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>105505</t>
+          <t>105407</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>112418</t>
+          <t>111978</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132210</t>
+          <t>131859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>211361</t>
+          <t>210572</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233713</t>
+          <t>234635</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>119247</t>
+          <t>118175</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131052</t>
+          <t>131016</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153753</t>
+          <t>154421</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169411</t>
+          <t>169863</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278626</t>
+          <t>278650</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297771</t>
+          <t>298139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60862</t>
+          <t>60684</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>84091</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>126267</t>
+          <t>124541</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126324</t>
+          <t>127556</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174546</t>
+          <t>176448</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>530466</t>
+          <t>530644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>555447</t>
+          <t>554457</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>651664</t>
+          <t>653390</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>693840</t>
+          <t>694734</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1194713</t>
+          <t>1192811</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1242935</t>
+          <t>1241703</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52052</t>
+          <t>57043</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47769</t>
+          <t>52663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54383</t>
+          <t>59514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54009</t>
+          <t>55675</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48553</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57871</t>
+          <t>59503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106061</t>
+          <t>112717</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99891</t>
+          <t>106577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110775</t>
+          <t>117658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25029</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33492</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>35668</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>26593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43119</t>
+          <t>45830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72627</t>
+          <t>79839</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>73151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76508</t>
+          <t>84452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>103963</t>
+          <t>108194</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95500</t>
+          <t>100380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110215</t>
+          <t>114807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>176589</t>
+          <t>188033</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>166581</t>
+          <t>177871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183839</t>
+          <t>197108</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>33571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61337</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56297</t>
+          <t>54575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65551</t>
+          <t>64223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>71523</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67448</t>
+          <t>66211</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77673</t>
+          <t>75846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>134515</t>
+          <t>131809</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127250</t>
+          <t>124564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140511</t>
+          <t>138071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>71900</t>
+          <t>80360</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68004</t>
+          <t>76791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73907</t>
+          <t>82506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>87003</t>
+          <t>92952</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81882</t>
+          <t>87639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91232</t>
+          <t>97392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>158903</t>
+          <t>173312</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153100</t>
+          <t>166326</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163940</t>
+          <t>178397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,27 +12139,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>15151</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29747</t>
+          <t>31324</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>27219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32272</t>
+          <t>33933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49445</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>46780</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52357</t>
+          <t>54623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,22 +12252,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>79192</t>
+          <t>82516</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74172</t>
+          <t>77300</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83036</t>
+          <t>86929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>13887</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>55302</t>
+          <t>55258</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51960</t>
+          <t>52195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57551</t>
+          <t>57755</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>51538</t>
+          <t>53422</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47190</t>
+          <t>49093</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55187</t>
+          <t>56992</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>106840</t>
+          <t>108679</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101555</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110975</t>
+          <t>113015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13713</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>23380</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>16755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54589</t>
+          <t>32457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>115493</t>
+          <t>141847</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109541</t>
+          <t>134252</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119776</t>
+          <t>146691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>318820</t>
+          <t>140743</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283992</t>
+          <t>131666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>334179</t>
+          <t>147368</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>434314</t>
+          <t>282589</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408944</t>
+          <t>271074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>454034</t>
+          <t>291056</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>338581</t>
+          <t>164123</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>338581</t>
+          <t>164123</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>338581</t>
+          <t>164123</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>461836</t>
+          <t>315464</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>461836</t>
+          <t>315464</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>461836</t>
+          <t>315464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17637</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>142070</t>
+          <t>157457</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137776</t>
+          <t>152077</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144661</t>
+          <t>160844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>174610</t>
+          <t>198765</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169005</t>
+          <t>191838</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>178856</t>
+          <t>203624</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>316680</t>
+          <t>356222</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>310349</t>
+          <t>348522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321941</t>
+          <t>362428</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>49651</t>
+          <t>52979</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39462</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>67575</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>120272</t>
+          <t>129855</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>68918</t>
+          <t>115502</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>156864</t>
+          <t>146572</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>169923</t>
+          <t>182834</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>110236</t>
+          <t>164800</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>201182</t>
+          <t>204185</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>600527</t>
+          <t>663412</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>588422</t>
+          <t>648816</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>610716</t>
+          <t>673920</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>912566</t>
+          <t>772464</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>875974</t>
+          <t>755747</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>963920</t>
+          <t>786817</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1513093</t>
+          <t>1435876</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1481834</t>
+          <t>1414525</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1572780</t>
+          <t>1453910</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
